--- a/master_template.xlsx
+++ b/master_template.xlsx
@@ -129,7 +129,7 @@
     <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,33 +175,49 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="13"/>
-      <color rgb="FF555555"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
-      <sz val="10"/>
+      <sz val="22"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FF2F5233"/>
+      <i val="true"/>
+      <sz val="13"/>
+      <color rgb="FFC9DFC2"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF1F3B21"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FF1F3B21"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="13"/>
-      <color rgb="FF2F5233"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FFC9DFC2"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -222,7 +238,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,20 +247,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4C7A47"/>
-        <bgColor rgb="FF555555"/>
+        <fgColor rgb="FF2F5233"/>
+        <bgColor rgb="FF1F3B21"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF5EC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F5233"/>
-        <bgColor rgb="FF555555"/>
+        <fgColor rgb="FFDCEAD5"/>
+        <bgColor rgb="FFC9DFC2"/>
       </patternFill>
     </fill>
   </fills>
@@ -257,17 +267,11 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FF2F5233"/>
       </bottom>
       <diagonal/>
     </border>
@@ -297,7 +301,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -314,59 +318,71 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -395,11 +411,11 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFCCCCCC"/>
+      <rgbColor rgb="FFC9DFC2"/>
       <rgbColor rgb="FF888888"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFEFF5EC"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -415,7 +431,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFDCEAD5"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -427,16 +443,16 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF555555"/>
+      <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF4C7A47"/>
+      <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF2F5233"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF2F5233"/>
+      <rgbColor rgb="FF1F3B21"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -738,7 +754,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -748,7 +764,7 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -768,7 +784,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
@@ -781,24 +797,28 @@
       <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
         <f aca="false">'Sales Tracker'!F19</f>
         <v>0</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <f aca="false">'Expense Tracker'!D19</f>
         <v>0</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <f aca="false">A6-B6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <f aca="false">IFERROR(A6/COUNTIF('Sales Tracker'!F3:F17,"&gt;0"),0)</f>
         <v>0</v>
       </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -842,206 +862,206 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12" t="n">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14" t="n">
         <f aca="false">IFERROR(D3*E3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12" t="n">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14" t="n">
         <f aca="false">IFERROR(D4*E4,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12" t="n">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14" t="n">
         <f aca="false">IFERROR(D5*E5,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12" t="n">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14" t="n">
         <f aca="false">IFERROR(D6*E6,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12" t="n">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14" t="n">
         <f aca="false">IFERROR(D7*E7,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12" t="n">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14" t="n">
         <f aca="false">IFERROR(D8*E8,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12" t="n">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14" t="n">
         <f aca="false">IFERROR(D9*E9,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12" t="n">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14" t="n">
         <f aca="false">IFERROR(D10*E10,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12" t="n">
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14" t="n">
         <f aca="false">IFERROR(D11*E11,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12" t="n">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14" t="n">
         <f aca="false">IFERROR(D12*E12,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12" t="n">
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14" t="n">
         <f aca="false">IFERROR(D13*E13,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12" t="n">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14" t="n">
         <f aca="false">IFERROR(D14*E14,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12" t="n">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14" t="n">
         <f aca="false">IFERROR(D15*E15,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12" t="n">
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14" t="n">
         <f aca="false">IFERROR(D16*E16,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12" t="n">
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14" t="n">
         <f aca="false">IFERROR(D17*E17,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="16" t="n">
         <f aca="false">SUM(F3:F17)</f>
         <v>0</v>
       </c>
@@ -1065,7 +1085,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -1074,123 +1094,127 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>27</v>
       </c>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="12"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="12"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="12"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="12"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="12"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="16" t="n">
         <f aca="false">SUM(D3:D17)</f>
         <v>0</v>
       </c>
@@ -1214,57 +1238,65 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="8"/>
-    </row>
-    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="9"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="5"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="19" t="n">
         <f aca="false">'Sales Tracker'!F19</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="19" t="n">
         <f aca="false">'Expense Tracker'!D19</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="19" t="n">
         <f aca="false">B4-B5</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="20" t="n">
         <f aca="false">IFERROR(B6/B4,0)</f>
         <v>0</v>
       </c>
